--- a/backend/data/financials_by_company/0090.HK.xlsx
+++ b/backend/data/financials_by_company/0090.HK.xlsx
@@ -3983,10 +3983,8 @@
           <t>Hangzhou</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>311108</t>
-        </is>
+      <c r="D2" t="n">
+        <v>311108</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -4105,7 +4103,7 @@
         <v>7.86</v>
       </c>
       <c r="AI2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AJ2" t="n">
         <v>9.699999999999999</v>
